--- a/PowerWeb/ExcelModels/TimeSheetCol.xlsx
+++ b/PowerWeb/ExcelModels/TimeSheetCol.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr date1904="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\PowerWeb\PowerWeb\PowerWeb\ExcelModels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Progetti\PowerWeb\PowerWeb\ExcelModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCEDD31-D66E-4E79-9165-ED298F6286BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="14400" windowHeight="11760"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
-    <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -181,6 +180,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -216,6 +232,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -391,7 +424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -562,22 +595,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>